--- a/WWP Planting iTree Project Parameters.xlsx
+++ b/WWP Planting iTree Project Parameters.xlsx
@@ -356,6 +356,9 @@
     <x:t>Annual carbon-dioxide sequestration; metric values use kilograms and imperial values use pounds.</x:t>
   </x:si>
   <x:si>
+    <x:t>OST_Planting, OST_Floors</x:t>
+  </x:si>
+  <x:si>
     <x:t>!_S_PLANTING_iTreeWater_RainfallInterceptedAnnual_Volume</x:t>
   </x:si>
   <x:si>
@@ -404,6 +407,81 @@
     <x:t>Unit System</x:t>
   </x:si>
   <x:si>
+    <x:t>!_S_PLANTING_LDS_Type_Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWP landscape data sheet type assigned via Floor Calculator (e.g. Lawn, Meadow, Granite - Blanco Cristal).</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_MatchKey_Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stable lookup key into the cached WWP landscape data sheet, used to re-find the exact coefficient row without re-matching.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PG_GENERAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_ResultSource_Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Whether the currently written values came from the coefficient table as calculated, or were edited manually in Floor Calculator before writing.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PG_ANALYSIS_RESULTS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_LastCalculated_Text</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISO 8601 date and time of the last Floor Calculator run for this element.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_CostSavedAnnual_Number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Estimated annual cost saved, from the WWP landscape data sheet's per-square-metre coefficient times this floor's area.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COST_SAVED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_OxygenProducedAnnual_Number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Estimated annual oxygen produced (kg), from the WWP landscape data sheet's per-square-metre coefficient times this floor's area.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oxygen levels O2 kg/yr (16/18 girth)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_TotalGWP_Number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Total global warming potential (product plus transport) from the WWP landscape data sheet's per-square-metre coefficient times this floor's area — an embodied-impact figure, not a benefit.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WWP_Total_GWP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_SurfaceTempReduction_Number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Surface temperature reduction for this landscape type, from the WWP landscape data sheet — an intrinsic material property, not scaled by area.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Surface_Temperature_Reduction_Min</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_AirTempReduction_Number</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air temperature reduction at 1.5m height for this landscape type, from the WWP landscape data sheet — an intrinsic material property, not scaled by area.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Air temperature reduction (1.5m height)</x:t>
+  </x:si>
+  <x:si>
     <x:t>WWP Planting / i-Tree Project Parameter Import</x:t>
   </x:si>
   <x:si>
@@ -473,13 +551,19 @@
     <x:t>Parameter groups</x:t>
   </x:si>
   <x:si>
-    <x:t>Identity Data = identity/location; Constraints = growth inputs; Geometry = live dimensions; Green Building = environmental results; Data = status and synchronization.</x:t>
+    <x:t>Groups now reflect functional role, not data type: Constraints = required manual input (necessary for calculation, provided by a person); Analysis Results = output (written back after calculation — i-Tree Calculator for trees, Floor Calculator for floors); Geometry = calculated (driven by family/growth formulas, not typed); General = optional (reference data, sync bookkeeping, overrides, display preferences).</x:t>
   </x:si>
   <x:si>
     <x:t>Important</x:t>
   </x:si>
   <x:si>
     <x:t>If a parameter already exists with the same name but another GUID, the importer will report it instead of replacing that definition.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Floor Calculator (phase 2)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>!_S_PLANTING_LDS_* parameters are bound to both OST_Planting and OST_Floors — Floor Calculator uses them on Floor elements (which represent planted/paved landscape areas, not building floors), and the same fields are available if a future update lets Planting instances fall back to the coefficient table too. !_S_PLANTING_LDS_Type_Text is the assigned WWP landscape data sheet type (search/match via Floor Calculator); results are computed client-side from that type's per-square-metre coefficients times the floor's area, except the two temperature-reduction fields which are intrinsic to the type and not scaled by area. Two result parameters (CO2 sequestered, avoided runoff) are shared with the existing i-Tree fields so trees and floors report through the same columns. There is no separate override parameter: Floor Calculator's own "Review values" dialog lets you check a metric as manual and type a different number before calculating — !_S_PLANTING_LDS_ResultSource_Text records whether a floor's values came from the coefficient table, a manual entry, or both.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2091,30 +2175,30 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H35" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J35" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10" ht="15" customHeight="1">
       <x:c r="A36" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B36" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E36" s="2" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F36" s="2" t="s">
         <x:v>102</x:v>
@@ -2134,19 +2218,19 @@
     </x:row>
     <x:row r="37" spans="1:10" ht="15" customHeight="1">
       <x:c r="A37" s="2" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B37" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E37" s="2" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B37" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C37" s="3" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D37" s="2" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="E37" s="2" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="F37" s="2" t="s">
         <x:v>102</x:v>
@@ -2155,24 +2239,24 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H37" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I37" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J37" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:10" ht="15" customHeight="1">
       <x:c r="A38" s="2" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="3" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
         <x:v>13</x:v>
@@ -2187,24 +2271,24 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H38" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I38" s="3" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="J38" s="2" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="J38" s="2" t="s">
-        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:10" ht="15" customHeight="1">
       <x:c r="A39" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C39" s="3" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
         <x:v>13</x:v>
@@ -2219,24 +2303,24 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H39" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I39" s="3" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="J39" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:10" ht="15" customHeight="1">
       <x:c r="A40" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B40" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C40" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
         <x:v>27</x:v>
@@ -2251,13 +2335,289 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H40" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I40" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="J40" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E41" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J41" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:10">
+      <x:c r="A42" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E42" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F42" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J42" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:10">
+      <x:c r="A43" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E43" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F43" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J43" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:10">
+      <x:c r="A44" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E44" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F44" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="J44" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:10">
+      <x:c r="A45" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E45" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F45" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="J45" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:10">
+      <x:c r="A46" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E46" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F46" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J46" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:10">
+      <x:c r="A47" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E47" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F47" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="J47" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:10">
+      <x:c r="A48" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E48" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F48" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="J48" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:10">
+      <x:c r="A49" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="E49" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F49" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J49" s="0" t="s">
+        <x:v>113</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2285,7 +2645,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="32" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B1" s="4"/>
       <x:c r="C1" s="4"/>
@@ -2295,23 +2655,23 @@
     </x:row>
     <x:row r="3" spans="1:6" ht="15" customHeight="1">
       <x:c r="A3" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6" ht="15" customHeight="1">
       <x:c r="A4" s="5" t="s">
-        <x:v>132</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>133</x:v>
+        <x:v>159</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6" ht="15" customHeight="1">
       <x:c r="A5" s="5" t="s">
-        <x:v>134</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B5" s="3" t="s">
         <x:v>11</x:v>
@@ -2319,82 +2679,90 @@
     </x:row>
     <x:row r="6" spans="1:6" ht="15" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>135</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6" ht="15" customHeight="1">
       <x:c r="A7" s="5" t="s">
-        <x:v>137</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>138</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6" ht="15" customHeight="1">
       <x:c r="A8" s="5" t="s">
-        <x:v>139</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:6" ht="15" customHeight="1">
       <x:c r="A9" s="5" t="s">
-        <x:v>141</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6" ht="15" customHeight="1">
       <x:c r="A10" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>144</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6" ht="15" customHeight="1">
       <x:c r="A11" s="5" t="s">
-        <x:v>145</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>146</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:6" ht="15" customHeight="1">
       <x:c r="A12" s="5" t="s">
-        <x:v>147</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B12" s="3" t="s">
-        <x:v>148</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6" ht="15" customHeight="1">
       <x:c r="A13" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>150</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:6" ht="15" customHeight="1">
       <x:c r="A14" s="5" t="s">
-        <x:v>151</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B14" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6" ht="15" customHeight="1">
       <x:c r="A15" s="5" t="s">
-        <x:v>153</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B15" s="3" t="s">
-        <x:v>154</x:v>
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>182</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
